--- a/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
+++ b/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>30/04/2025</t>
+    <t>15/05/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -86,7 +86,7 @@
     <t>OBSERVACIONES</t>
   </si>
   <si>
-    <t xml:space="preserve">Desktop </t>
+    <t>Desktop</t>
   </si>
   <si>
     <t>DELL</t>
@@ -101,7 +101,7 @@
     <t>DVZ-VH-TI-00192</t>
   </si>
   <si>
-    <t xml:space="preserve">Fuente alimentacion </t>
+    <t>Fuente de alimentación</t>
   </si>
   <si>
     <t>HA90PM190</t>
@@ -140,6 +140,27 @@
     <t>CN-065K5F-LO300-3A9-0E6X</t>
   </si>
   <si>
+    <t>Pantalla TV</t>
+  </si>
+  <si>
+    <t>Lg</t>
+  </si>
+  <si>
+    <t>dasdsdasdsadssss</t>
+  </si>
+  <si>
+    <t>SASASASASASASAS</t>
+  </si>
+  <si>
+    <t>Impresora de Tarjetas</t>
+  </si>
+  <si>
+    <t>DADSADSAD</t>
+  </si>
+  <si>
+    <t>DSADASD</t>
+  </si>
+  <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
   </si>
   <si>
@@ -173,7 +194,7 @@
     <t>Alejandro Cancino Arguello</t>
   </si>
   <si>
-    <t>Supervisor TI</t>
+    <t>Coordinador de TI</t>
   </si>
 </sst>
 </file>
@@ -1106,80 +1127,96 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="15">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
+      <c r="A25" s="38">
+        <v>6</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="15">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
+      <c r="A26" s="38">
+        <v>7</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
+      <c r="A29" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
       <c r="A31" s="28" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -1190,23 +1227,22 @@
       <c r="H31" s="28"/>
       <c r="I31" s="28"/>
     </row>
-    <row r="32" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A32" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" customHeight="1" ht="27">
+    <row r="32" spans="1:10" customHeight="1" ht="15">
+      <c r="A32" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" customHeight="1" ht="15">
       <c r="A33" s="28" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
@@ -1217,96 +1253,101 @@
       <c r="H33" s="28"/>
       <c r="I33" s="28"/>
     </row>
-    <row r="34" spans="1:10" customHeight="1" ht="15">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="39">
-      <c r="A35" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+    <row r="34" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A34" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="27">
+      <c r="A35" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="32"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="15">
-      <c r="A37" s="2"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="39">
+      <c r="A37" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
     </row>
     <row r="38" spans="1:10" customHeight="1" ht="15">
       <c r="A38" s="32"/>
-      <c r="B38" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
       <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
-        <v>49</v>
-      </c>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="2"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
+      <c r="G40" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="D41" s="36" t="s">
+        <v>56</v>
+      </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -1315,68 +1356,90 @@
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="34" t="str">
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+    </row>
+    <row r="43" spans="1:10" customHeight="1" ht="15">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" customHeight="1" ht="15">
+      <c r="A44" s="2"/>
+      <c r="B44" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="34" t="str">
         <f>C10</f>
         <v>Rednar García Harcía</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-    </row>
-    <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="34" t="str">
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+    </row>
+    <row r="45" spans="1:10" customHeight="1" ht="15">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="34" t="str">
         <f>C12</f>
         <v>Auxiliar Predictivo</v>
       </c>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-    </row>
-    <row r="44" spans="1:10" customHeight="1" ht="15">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" customHeight="1" ht="15">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
-      <c r="A46" s="32"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:10" customHeight="1" ht="15">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" customHeight="1" ht="15">
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1395,23 +1458,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="G42:I42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="G45:I45"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1430,7 +1493,13 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H19:I24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H19:I26"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
+++ b/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>15/05/2025</t>
+    <t>16/06/2025</t>
   </si>
   <si>
     <t>Nombre:</t>
@@ -159,6 +159,39 @@
   </si>
   <si>
     <t>DSADASD</t>
+  </si>
+  <si>
+    <t>ACCESSPOINT</t>
+  </si>
+  <si>
+    <t>erdtf6y</t>
+  </si>
+  <si>
+    <t>EDTRYUJGIH</t>
+  </si>
+  <si>
+    <t>Camara Fija</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>trctvuyi</t>
+  </si>
+  <si>
+    <t>TYBUI</t>
+  </si>
+  <si>
+    <t>Adaptador VGA a HDMI</t>
+  </si>
+  <si>
+    <t>KOBLENZ</t>
+  </si>
+  <si>
+    <t>rfyguih</t>
+  </si>
+  <si>
+    <t>RCTYUBIJO</t>
   </si>
   <si>
     <t>MEDIANTE ESTE DOCUMENTO ASUMO LAS SIGUIENTES RESPONSABILIDADES:</t>
@@ -1169,107 +1202,130 @@
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="15">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
+      <c r="A27" s="38">
+        <v>8</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="15">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
+      <c r="A28" s="38">
+        <v>9</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="15">
-      <c r="A29" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
+      <c r="A29" s="38">
+        <v>10</v>
+      </c>
+      <c r="B29" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="15">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="15">
-      <c r="A31" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
     </row>
     <row r="32" spans="1:10" customHeight="1" ht="15">
-      <c r="A32" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
+      <c r="A32" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
     </row>
     <row r="33" spans="1:10" customHeight="1" ht="15">
-      <c r="A33" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-    </row>
-    <row r="34" spans="1:10" customHeight="1" ht="24.05">
-      <c r="A34" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" customHeight="1" ht="27">
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="27"/>
+    </row>
+    <row r="34" spans="1:10" customHeight="1" ht="15">
+      <c r="A34" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" customHeight="1" ht="15">
       <c r="A35" s="28" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
@@ -1281,132 +1337,129 @@
       <c r="I35" s="28"/>
     </row>
     <row r="36" spans="1:10" customHeight="1" ht="15">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-    </row>
-    <row r="37" spans="1:10" customHeight="1" ht="39">
-      <c r="A37" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-    </row>
-    <row r="38" spans="1:10" customHeight="1" ht="15">
-      <c r="A38" s="32"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
+      <c r="A36" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+    </row>
+    <row r="37" spans="1:10" customHeight="1" ht="24.05">
+      <c r="A37" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" customHeight="1" ht="27">
+      <c r="A38" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
     </row>
     <row r="39" spans="1:10" customHeight="1" ht="15">
-      <c r="A39" s="2"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-    </row>
-    <row r="40" spans="1:10" customHeight="1" ht="15">
-      <c r="A40" s="32"/>
-      <c r="B40" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+    </row>
+    <row r="40" spans="1:10" customHeight="1" ht="39">
+      <c r="A40" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
     </row>
     <row r="41" spans="1:10" customHeight="1" ht="15">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="36" t="s">
-        <v>56</v>
-      </c>
+      <c r="A41" s="32"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
     </row>
     <row r="42" spans="1:10" customHeight="1" ht="15">
       <c r="A42" s="2"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:10" customHeight="1" ht="15">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
+      <c r="G43" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
     </row>
     <row r="44" spans="1:10" customHeight="1" ht="15">
       <c r="A44" s="2"/>
-      <c r="B44" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="36" t="s">
+        <v>67</v>
+      </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="34" t="str">
-        <f>C10</f>
-        <v>Rednar García Harcía</v>
-      </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
     </row>
     <row r="45" spans="1:10" customHeight="1" ht="15">
       <c r="A45" s="2"/>
-      <c r="B45" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="34" t="str">
-        <f>C12</f>
-        <v>Auxiliar Predictivo</v>
-      </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
     </row>
     <row r="46" spans="1:10" customHeight="1" ht="15">
       <c r="A46" s="2"/>
@@ -1415,31 +1468,74 @@
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
     </row>
     <row r="47" spans="1:10" customHeight="1" ht="15">
       <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="B47" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
+      <c r="G47" s="34" t="str">
+        <f>C10</f>
+        <v>Rednar García Harcía</v>
+      </c>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
     </row>
     <row r="48" spans="1:10" customHeight="1" ht="15">
-      <c r="A48" s="32"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
+      <c r="G48" s="34" t="str">
+        <f>C12</f>
+        <v>Auxiliar Predictivo</v>
+      </c>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+    </row>
+    <row r="49" spans="1:10" customHeight="1" ht="15">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:10" customHeight="1" ht="15">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" customHeight="1" ht="15">
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
     </row>
     <row r="1048575" spans="1:10" customHeight="1" ht="12.8"/>
   </sheetData>
@@ -1458,23 +1554,23 @@
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="H18:I18"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A34:I34"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A36:I36"/>
     <mergeCell ref="A37:I37"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="G44:I44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="G45:I45"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="G43:I43"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="G48:I48"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
@@ -1499,7 +1595,16 @@
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H19:I26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H19:I29"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.51181102362205" footer="0.51181102362205"/>

--- a/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
+++ b/database/controller_excel/Resguardo_Rednar_García_Harcía.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="72">
   <si>
     <t>SERVICIOS PETROLEROS TERRESTES</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Fecha:</t>
   </si>
   <si>
-    <t>25/06/2025</t>
+    <t>30/06/2025</t>
   </si>
   <si>
     <t>Área:</t>
   </si>
   <si>
-    <t>Recursos Humanos</t>
+    <t>TI</t>
   </si>
   <si>
     <t>Región:</t>
@@ -225,6 +225,12 @@
   </si>
   <si>
     <t>Auxiliar Predictivo</t>
+  </si>
+  <si>
+    <t>Rodrigo Canseco</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
   </si>
 </sst>
 </file>
@@ -891,7 +897,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="12.5546875" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="true" style="0"/>
@@ -1591,6 +1597,26 @@
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="F52" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="F56" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="F57" s="22" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>
